--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:26:54+00:00</t>
+    <t>2025-01-23T13:26:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2229,7 +2229,7 @@
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>74</v>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T13:26:37+00:00</t>
+    <t>2025-01-24T17:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T17:22:23+00:00</t>
+    <t>2025-01-29T14:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T14:25:50+00:00</t>
+    <t>2025-01-29T15:50:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T15:50:40+00:00</t>
+    <t>2025-01-30T15:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T15:03:39+00:00</t>
+    <t>2025-01-31T08:45:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T08:45:39+00:00</t>
+    <t>2025-02-18T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="189">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Structure pour le compte de laquelle intervient le professionnel.</t>
+    <t>L'élément de l'en-tête du CDA representedOrganization permet de représenter la structure pour le compte de laquelle intervient le professionnel.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -409,6 +409,12 @@
     <t>Organization.id</t>
   </si>
   <si>
+    <t>Identifiant de la structure : 
+- Si le responsable est un professionnel : Identifiant de la structure pour le compte de laquelle intervient le professionnel. 
+- Si le responsable est un SNR : SIREN de l'éditeur. 
+- Si le responsable est le DP : Identifiant du DP.</t>
+  </si>
+  <si>
     <t>Organization.name</t>
   </si>
   <si>
@@ -416,6 +422,12 @@
 </t>
   </si>
   <si>
+    <t>Nom de la structure : 
+- Si le responsable est un professionnel : Nom de la structure. 
+- Si le responsable est un SNR : Nom de l'éditeur. 
+- Si le responsable est le DP : Dossier Pharmaceutique.</t>
+  </si>
+  <si>
     <t>Organization.telecom</t>
   </si>
   <si>
@@ -423,6 +435,12 @@
 </t>
   </si>
   <si>
+    <t>Coordonnées télécom de la structure :  
+- Si le responsable est un professionnel : Coordonnées télécom de la structure. 
+- Si le responsable est un SNR : non renseigné. 
+- Si le responsable est le DP : non renseigné.</t>
+  </si>
+  <si>
     <t>Organization.addr</t>
   </si>
   <si>
@@ -430,6 +448,12 @@
 </t>
   </si>
   <si>
+    <t>Adresse géopostale de la structure : 
+- Si le responsable est un professionnel : Adresse géopostale de la structure. 
+- Si le responsable est un SNR : non renseigné. 
+- Si le responsable est le DP : non renseigné.</t>
+  </si>
+  <si>
     <t>Organization.standardIndustryClassCode</t>
   </si>
   <si>
@@ -437,7 +461,149 @@
 </t>
   </si>
   <si>
+    <t>Cadre d'exercice du professionnel : 
+- Si le responsable est un professionnel : Cadre d'exercice. 
+- Si le responsable est un SNR : non renseigné. 
+- Si le responsable est le DP : non renseigné.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-OrganizationIndustryClassNAICS</t>
+  </si>
+  <si>
+    <t>Organization.standardIndustryClassCode.nullFlavor</t>
+  </si>
+  <si>
+    <t>Organization.standardIndustryClassCode.code</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J04-XdsPracticeSettingCode-CISIS/FHIR/JDV-J04-XdsPracticeSettingCode-CISIS</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Organization.standardIndustryClassCode.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Organization.standardIndustryClassCode.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Organization.standardIndustryClassCode.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Organization.standardIndustryClassCode.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Organization.standardIndustryClassCode.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Organization.standardIndustryClassCode.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Organization.standardIndustryClassCode.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
+</t>
+  </si>
+  <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>Organization.standardIndustryClassCode.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>Organization.standardIndustryClassCode.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CD
+</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
   </si>
   <si>
     <t>Organization.asOrganizationPartOf</t>
@@ -746,11 +912,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK19"/>
+  <dimension ref="A1:AK30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.359375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.359375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.1015625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="58.1015625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="24.9375" customWidth="true" bestFit="true"/>
@@ -2144,7 +2310,9 @@
       <c r="K14" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L14" s="2"/>
+      <c r="L14" t="s" s="2">
+        <v>129</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2215,10 +2383,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2241,9 +2409,11 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="L15" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2294,7 +2464,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2314,10 +2484,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2340,9 +2510,11 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="L16" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2393,7 +2565,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2413,10 +2585,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2439,9 +2611,11 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L17" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2492,7 +2666,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2512,10 +2686,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2538,9 +2712,11 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L18" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2567,11 +2743,11 @@
         <v>74</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>74</v>
@@ -2589,7 +2765,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2609,21 +2785,23 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E19" s="2"/>
+      <c r="E19" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>74</v>
@@ -2635,10 +2813,12 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
+      <c r="M19" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -2664,13 +2844,11 @@
         <v>74</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>74</v>
@@ -2688,7 +2866,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>138</v>
+        <v>89</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2703,6 +2881,1129 @@
         <v>74</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L20" s="2"/>
+      <c r="M20" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y20" s="2"/>
+      <c r="Z20" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L21" s="2"/>
+      <c r="M21" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L22" s="2"/>
+      <c r="M22" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L23" s="2"/>
+      <c r="M23" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L24" s="2"/>
+      <c r="M24" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L25" s="2"/>
+      <c r="M25" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L26" s="2"/>
+      <c r="M26" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L27" s="2"/>
+      <c r="M27" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L28" s="2"/>
+      <c r="M28" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L29" s="2"/>
+      <c r="M29" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK30" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T15:18:09+00:00</t>
+    <t>2025-02-23T14:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-23T14:02:58+00:00</t>
+    <t>2025-02-24T10:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:33:29+00:00</t>
+    <t>2025-02-24T11:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:08:59+00:00</t>
+    <t>2025-02-24T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T14:08:41+00:00</t>
+    <t>2025-02-25T09:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
